--- a/resources/nessus/Nessus_VulnLab_scan-a.xlsx
+++ b/resources/nessus/Nessus_VulnLab_scan-a.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,10 +529,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H2" t="n">
+        <v>80</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -604,10 +602,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H3" t="n">
+        <v>22</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -679,10 +675,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H4" t="n">
+        <v>5432</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -754,10 +748,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H5" t="n">
+        <v>5432</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -829,10 +821,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H6" t="n">
+        <v>5432</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -904,10 +894,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H7" t="n">
+        <v>445</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -979,10 +967,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
+      <c r="H8" t="n">
+        <v>513</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1054,10 +1040,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
+      <c r="H9" t="n">
+        <v>514</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1129,10 +1113,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H10" t="n">
+        <v>80</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1204,10 +1186,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H11" t="n">
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1279,10 +1259,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H12" t="n">
+        <v>445</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1354,10 +1332,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H13" t="n">
+        <v>22</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1429,10 +1405,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H14" t="n">
+        <v>5432</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1504,10 +1478,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H15" t="n">
+        <v>5432</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1579,10 +1551,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H16" t="n">
+        <v>5432</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1654,10 +1624,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H17" t="n">
+        <v>5432</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1729,10 +1697,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H18" t="n">
+        <v>5432</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1804,10 +1770,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H19" t="n">
+        <v>5432</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1879,10 +1843,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="H20" t="n">
+        <v>23</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1954,10 +1916,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H21" t="n">
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2029,10 +1989,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H22" t="n">
+        <v>22</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2104,10 +2062,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H23" t="n">
+        <v>22</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2179,10 +2135,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H24" t="n">
+        <v>22</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2254,10 +2208,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H25" t="n">
+        <v>5432</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2329,10 +2281,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H26" t="n">
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2404,10 +2354,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H27" t="n">
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2479,10 +2427,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H28" t="n">
+        <v>80</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2554,10 +2500,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H29" t="n">
+        <v>80</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2629,10 +2573,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H30" t="n">
+        <v>22</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2704,10 +2646,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H31" t="n">
+        <v>80</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2779,10 +2719,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H32" t="n">
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2854,10 +2792,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H33" t="n">
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2929,10 +2865,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H34" t="n">
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3004,10 +2938,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H35" t="n">
+        <v>21</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3079,10 +3011,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H36" t="n">
+        <v>80</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3154,10 +3084,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H37" t="n">
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3229,10 +3157,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H38" t="n">
+        <v>80</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3304,10 +3230,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H39" t="n">
+        <v>445</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3379,10 +3303,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H40" t="n">
+        <v>445</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3454,10 +3376,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="H41" t="n">
+        <v>139</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3529,10 +3449,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H42" t="n">
+        <v>445</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3604,10 +3522,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H43" t="n">
+        <v>445</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3679,10 +3595,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H44" t="n">
+        <v>445</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3754,10 +3668,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H45" t="n">
+        <v>3306</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3829,10 +3741,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H46" t="n">
+        <v>21</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3904,10 +3814,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H47" t="n">
+        <v>22</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3979,10 +3887,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="H48" t="n">
+        <v>23</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4054,10 +3960,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H49" t="n">
+        <v>80</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4129,10 +4033,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="H50" t="n">
+        <v>139</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4204,10 +4106,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H51" t="n">
+        <v>445</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -4279,10 +4179,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
+      <c r="H52" t="n">
+        <v>512</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -4354,10 +4252,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
+      <c r="H53" t="n">
+        <v>513</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4429,10 +4325,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
+      <c r="H54" t="n">
+        <v>514</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -4504,10 +4398,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>1524</t>
-        </is>
+      <c r="H55" t="n">
+        <v>1524</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4579,10 +4471,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H56" t="n">
+        <v>3306</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -4654,10 +4544,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H57" t="n">
+        <v>5432</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4729,10 +4617,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H58" t="n">
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4804,10 +4690,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H59" t="n">
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4879,10 +4763,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H60" t="n">
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4954,10 +4836,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H61" t="n">
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5029,10 +4909,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H62" t="n">
+        <v>22</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5104,10 +4982,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H63" t="n">
+        <v>5432</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5179,10 +5055,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H64" t="n">
+        <v>80</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5254,10 +5128,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H65" t="n">
+        <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5329,10 +5201,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H66" t="n">
+        <v>5432</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5404,10 +5274,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H67" t="n">
+        <v>5432</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5479,10 +5347,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H68" t="n">
+        <v>22</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5554,10 +5420,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H69" t="n">
+        <v>5432</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5629,10 +5493,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H70" t="n">
+        <v>22</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5704,10 +5566,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H71" t="n">
+        <v>22</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5779,10 +5639,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H72" t="n">
+        <v>22</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -5854,10 +5712,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H73" t="n">
+        <v>22</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -5929,10 +5785,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H74" t="n">
+        <v>22</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6004,10 +5858,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H75" t="n">
+        <v>5432</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6079,10 +5931,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H76" t="n">
+        <v>5432</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6154,10 +6004,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H77" t="n">
+        <v>5432</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6181,7 +6029,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>['Subject Name:', 'Country: XX\nState/Province: There is no such thing outside US\nLocality: Everywhere\nOrganization: OCOSA\nOrganization Unit: Office for Complication of Otherwise Simple Affairs\nCommon Name: ubuntu804-base.localdomain\nEmail Address: root@ubuntu804-base.localdomain', 'Issuer Name:', 'Country: XX\nState/Province: There is no such thing outside US\nLocality: Everywhere\nOrganization: OCOSA\nOrganization Unit: Office for Complication of Otherwise Simple Affairs\nCommon Name: ubuntu804-base.localdomain\nEmail Address: root@ubuntu804-base.localdomain', 'Serial Number: 00 FA F9 3A 4C 7F B6 B9 CC', 'Version: 1', 'Signature Algorithm: SHA-1 With RSA Encryption', 'Not Valid Before: Mar 17 14:07:45 2010 GMT\nNot Valid After: Apr 16 14:07:45 2010 GMT', 'Public Key Info:', 'Algorithm: RSA Encryption\nKey Length: 1024 bits\nPublic Key: 00 D6 B4 13 36 33 9A 95 71 7B 1B DE 7C 83 75 DA 71 B1 3C A9 \n            7F FE AD 64 1B 77 E9 4F AE BE CA D4 F8 CB EF AE BB 43 79 24 \n            73 FF 3C E5 9E 3B 6D FC C8 B1 AC FA 4C 4D 5E 9B 4C 99 54 0B \n            D7 A8 4A 50 BA A9 DE 1D 1F F4 E4 6B 02 A3 F4 6B 45 CD 4C AF \n            8D 89 62 33 8F 65 BB 36 61 9F C4 2C 73 C1 4E 2E A0 A8 14 4E \n            98 70 46 61 BB D1 B9 31 DF 8C 99 EE 75 6B 79 3C 40 A0 AE 97 \n            00 90 9D DC 99 0D 33 A4 B5 \nExponent: 01 00 01', 'Signature Length: 128 bytes / 1024 bits\nSignature: 00 92 A4 B4 B8 14 55 63 25 51 4A 0B C3 2A 22 CF 3A F8 17 6A \n           0C CF 66 AA A7 65 2F 48 6D CD E3 3E 5C 9F 77 6C D4 44 54 1F \n           1E 84 4F 8E D4 8D DD AC 2D 88 09 21 A8 DA 56 2C A9 05 3C 49 \n           68 35 19 75 0C DA 53 23 88 88 19 2D 74 26 C1 22 65 EE 11 68 \n           83 6A 53 4A 9C 27 CB A0 B4 E9 8D 29 0C B2 3C 18 5C 67 CC 53 \n           A6 1E 30 D0 AA 26 7B 1E AE 40 B9 29 01 6C 2E BC A2 19 94 7C \n           15 6E 8D 30 38 F6 CA 2E 75', 'Fingerprints :', 'SHA-256 Fingerprint: E7 A7 FA 0D 63 E4 57 C7 C4 A5 9B 38 B7 08 49 C6 A7 0B DA 6F \n                     83 0C 7A F1 E3 2D EE 43 6D E8 13 CC \nSHA-1 Fingerprint: ED 09 30 88 70 66 03 BF D5 DC 23 73 99 B4 98 DA 2D 4D 31 C6 \nMD5 Fingerprint: DC D9 AD 90 6C 8F 2F 73 74 AF 38 3B 25 40 88 28', 'PEM certificate :', '-----BEGIN CERTIFICATE-----\nMIIDWzCCAsQCCQD6+TpMf7a5zDANBgkqhkiG9w0BAQUFADCB8TELMAkGA1UEBhMCWFgxKjAoBgNVBAgTIVRoZXJlIGlzIG5vIHN1Y2ggdGhpbmcgb3V0c2lkZSBVUzETMBEGA1UEBxMKRXZlcnl3aGVyZTEOMAwGA1UEChMFT0NPU0ExPDA6BgNVBAsTM09mZmljZSBmb3IgQ29tcGxpY2F0aW9uIG9mIE90aGVyd2lzZSBTaW1wbGUgQWZmYWlyczEjMCEGA1UEAxMadWJ1bnR1ODA0LWJhc2UubG9jYWxkb21haW4xLjAsBgkqhkiG9w0BCQEWH3Jvb3RAdWJ1bnR1ODA0LWJhc2UubG9jYWxkb21haW4wHhcNMTAwMzE3MTQwNzQ1WhcNMTAwNDE2MTQwNzQ1WjCB8TELMAkGA1UEBhMCWFgxKjAoBgNVBAgTIVRoZXJlIGlzIG5vIHN1Y2ggdGhpbmcgb3V0c2lkZSBVUzETMBEGA1UEBxMKRXZlcnl3aGVyZTEOMAwGA1UEChMFT0NPU0ExPDA6BgNVBAsTM09mZmljZSBmb3IgQ29tcGxpY2F0aW9uIG9mIE90aGVyd2lzZSBTaW1wbGUgQWZmYWlyczEjMCEGA1UEAxMadWJ1bnR1ODA0LWJhc2UubG9jYWxkb21haW4xLjAsBgkqhkiG9w0BCQEWH3Jvb3RAdWJ1bnR1ODA0LWJhc2UubG9jYWxkb21haW4wgZ8wDQYJKoZIhvcNAQEBBQADgY0AMIGJAoGBANa0EzYzmpVxexvefIN12nGxPKl//q1kG3fpT66+ytT4y++uu0N5JHP/POWeO238yLGs+kxNXptMmVQL16hKULqp3h0f9ORrAqP0a0XNTK+NiWIzj2W7NmGfxCxzwU4uoKgUTphwRmG70bkx34yZ7nVreTxAoK6XAJCd3JkNM6S1AgMBAAEwDQYJKoZIhvcNAQEFBQADgYEAkqS0uBRVYyVRSgvDKiLPOvgXagzPZqqnZS9Ibc3jPlyfd2zURFQfHoRPjtSN3awtiAkhqNpWLKkFPEloNRl1DNpTI4iIGS10JsEiZe4RaINqU0qcJ8ugtOmNKQyyPBhcZ8xTph4w0Komex6uQLkpAWwuvKIZlHwVbo0wOPbKLnU=\n-----END CERTIFICATE-----']</t>
+          <t>['Subject Name:', 'Country: XX\nState/Province: There is no such thing outside US\nLocality: Everywhere\nOrganization: OCOSA\nOrganization Unit: Office for Complication of Otherwise Simple Affairs\nCommon Name: ubuntu804-base.localdomain\nEmail Address: root@ubuntu804-base.localdomain', 'Issuer Name:', 'Country: XX\nState/Province: There is no such thing outside US\nLocality: Everywhere\nOrganization: OCOSA\nOrganization Unit: Office for Complication of Otherwise Simple Affairs\nCommon Name: ubuntu804-base.localdomain\nEmail Address: root@ubuntu804-base.localdomain', 'Serial Number: 00 FA F9 3A 4C 7F B6 B9 CC', 'Version: 1', 'Signature Algorithm: SHA-1 With RSA Encryption', 'Not Valid Before: Mar 17 14:07:45 2010 GMT\nNot Valid After: Apr 16 14:07:45 2010 GMT', 'Public Key Info:', 'Algorithm: RSA Encryption\nKey Length: 1024 bits\nPublic Key: 00 D6 B4 13 36 33 9A 95 71 7B 1B DE 7C 83 75 DA 71 B1 3C A9 \n            7F FE AD 64 1B 77 E9 4F AE BE CA D4 F8 CB EF AE BB 43 79 24 \n            73 FF 3C E5 9E 3B 6D FC C8 B1 AC FA 4C 4D 5E 9B 4C 99 54 0B \n            D7 A8 4A 50 BA A9 DE 1D 1F F4 E4 6B 02 A3 F4 6B 45 CD 4C AF \n            8D 89 62 33 8F 65 BB 36 61 9F C4 2C 73 C1 4E 2E A0 A8 14 4E \n            98 70 46 61 BB D1 B9 31 DF 8C 99 EE 75 6B 79 3C 40 A0 AE 97 \n            00 90 9D DC 99 0D 33 A4 B5 \nExponent: 01 00 01', 'Signature Length: 128 bytes / 1024 bits\nSignature: 00 92 A4 B4 B8 14 55 63 25 51 4A 0B C3 2A 22 CF 3A F8 17 6A \n           0C CF 66 AA A7 65 2F 48 6D CD E3 3E 5C 9F 77 6C D4 44 54 1F \n           1E 84 4F 8E D4 8D DD AC 2D 88 09 21 A8 DA 56 2C A9 05 3C 49 \n           68 35 19 75 0C DA 53 23 88 88 19 2D 74 26 C1 22 65 EE 11 68 \n           83 6A 53 4A 9C 27 CB A0 B4 E9 8D 29 0C B2 3C 18 5C 67 CC 53 \n           A6 1E 30 D0 AA 26 7B 1E AE 40 B9 29 01 6C 2E BC A2 19 94 7C \n           15 6E 8D 30 38 F6 CA 2E 75', 'Fingerprints :', 'SHA-256 Fingerprint: E7 A7 FA 0D 63 E4 57 C7 C4 A5 9B 38 B7 08 49 C6 A7 0B DA 6F \n                     83 0C 7A F1 E3 2D EE 43 6D E8 13 CC \nSHA-1 Fingerprint: ED 09 30 88 70 66 03 BF D5 DC 23 73 99 B4 98 DA 2D 4D 31 C6 \nMD5 Fingerprint: DC D9 AD 90 6C 8F 2F 73 74 AF 38 3B 25 40 88 28']</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -6229,10 +6077,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H78" t="n">
+        <v>5432</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6304,10 +6150,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H79" t="n">
+        <v>5432</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6331,7 +6175,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>['Here is the list of SSL ciphers supported by the remote server :\nEach group is reported per SSL Version.', 'SSL Version : TLSv1\n  Medium Strength Ciphers (&gt; 64-bit and &lt; 112-bit key, or 3DES)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    EDH-RSA-DES-CBC3-SHA          0x00, 0x16       DHE           RSA      3DES-CBC(168)          SHA1\n    DES-CBC3-SHA                  0x00, 0x0A       RSA           RSA      3DES-CBC(168)          SHA1', 'High Strength Ciphers (&gt;= 112-bit key)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    DHE-RSA-AES128-SHA            0x00, 0x33       DHE           RSA      AES-CBC(128)           SHA1\n    DHE-RSA-AES256-SHA            0x00, 0x39       DHE           RSA      AES-CBC(256)           SHA1\n    AES128-SHA                    0x00, 0x2F       RSA           RSA      AES-CBC(128)           SHA1\n    AES256-SHA                    0x00, 0x35       RSA           RSA      AES-CBC(256)           SHA1\n    RC4-SHA                       0x00, 0x05       RSA           RSA      RC4(128)               SHA1', 'SSL Version : SSLv3\n  Medium Strength Ciphers (&gt; 64-bit and &lt; 112-bit key, or 3DES)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    EDH-RSA-DES-CBC3-SHA          0x00, 0x16       DHE           RSA      3DES-CBC(168)          SHA1\n    DES-CBC3-SHA                  0x00, 0x0A       RSA           RSA      3DES-CBC(168)          SHA1', 'High Strength Ciphers (&gt;= 112-bit key)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    DHE-RSA-AES128-SHA            0x00, 0x33       DHE           RSA      AES-CBC(128)           SHA1\n    DHE-RSA-AES256-SHA            0x00, 0x39       DHE           RSA      AES-CBC(256)           SHA1\n    AES128-SHA                    0x00, 0x2F       RSA           RSA      AES-CBC(128)           SHA1\n    AES256-SHA                    0x00, 0x35       RSA           RSA      AES-CBC(256)           SHA1\n    RC4-SHA                       0x00, 0x05       RSA           RSA      RC4(128)               SHA1', 'The fields above are :', '{Tenable ciphername}\n  {Cipher ID code}\n  Kex={key exchange}\n  Auth={authentication}\n  Encrypt={symmetric encryption method}\n  MAC={message authentication code}\n  {export flag}', 'Note that this service does not encrypt traffic by default but does\nsupport upgrading to an encrypted connection using STARTTLS.']</t>
+          <t>['Here is the list of SSL ciphers supported by the remote server :\nEach group is reported per SSL Version.', 'SSL Version : TLSv1\n  Medium Strength Ciphers (&gt; 64-bit and &lt; 112-bit key, or 3DES)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    EDH-RSA-DES-CBC3-SHA          0x00, 0x16       DHE           RSA      3DES-CBC(168)          SHA1\n    DES-CBC3-SHA                  0x00, 0x0A       RSA           RSA      3DES-CBC(168)          SHA1', 'High Strength Ciphers (&gt;= 112-bit key)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    DHE-RSA-AES128-SHA            0x00, 0x33       DHE           RSA      AES-CBC(128)           SHA1\n    DHE-RSA-AES256-SHA            0x00, 0x39       DHE           RSA      AES-CBC(256)           SHA1\n    AES128-SHA                    0x00, 0x2F       RSA           RSA      AES-CBC(128)           SHA1\n    AES256-SHA                    0x00, 0x35       RSA           RSA      AES-CBC(256)           SHA1\n    RC4-SHA                       0x00, 0x05       RSA           RSA      RC4(128)               SHA1', 'SSL Version : SSLv3\n  Medium Strength Ciphers (&gt; 64-bit and &lt; 112-bit key, or 3DES)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    EDH-RSA-DES-CBC3-SHA          0x00, 0x16       DHE           RSA      3DES-CBC(168)          SHA1\n    DES-CBC3-SHA                  0x00, 0x0A       RSA           RSA      3DES-CBC(168)          SHA1', 'High Strength Ciphers (&gt;= 112-bit key)', 'Name                          Code             KEX           Auth     Encryption             MAC\n    ----------------------        ----------       ---           ----     ---------------------  ---\n    DHE-RSA-AES128-SHA            0x00, 0x33       DHE           RSA      AES-CBC(128)           SHA1\n    DHE-RSA-AES256-SHA            0x00, 0x39       DHE           RSA      AES-CBC(256)           SHA1\n    AES128-SHA                    0x00, 0x2F       RSA           RSA      AES-CBC(128)           SHA1\n    AES256-SHA                    0x00, 0x35       RSA           RSA      AES-CBC(256)           SHA1\n    RC4-SHA                       0x00, 0x05       RSA           RSA      RC4(128)               SHA1']</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -6379,10 +6223,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H80" t="n">
+        <v>5432</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6454,10 +6296,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H81" t="n">
+        <v>5432</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6529,10 +6369,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
+      <c r="H82" t="n">
+        <v>5432</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -6604,10 +6442,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H83" t="n">
+        <v>445</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -6679,10 +6515,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H84" t="n">
+        <v>445</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -6754,10 +6588,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H85" t="n">
+        <v>445</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -6829,10 +6661,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H86" t="n">
+        <v>21</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6904,10 +6734,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H87" t="n">
+        <v>22</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -6979,10 +6807,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="H88" t="n">
+        <v>23</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -7054,10 +6880,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H89" t="n">
+        <v>80</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -7129,10 +6953,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H90" t="n">
+        <v>3306</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -7204,10 +7026,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H91" t="n">
+        <v>0</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -7279,10 +7099,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H92" t="n">
+        <v>0</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -7354,10 +7172,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="H93" t="n">
+        <v>69</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -7429,10 +7245,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H94" t="n">
+        <v>0</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7504,10 +7318,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="H95" t="n">
+        <v>23</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -7579,10 +7391,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H96" t="n">
+        <v>0</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -7654,10 +7464,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>1524</t>
-        </is>
+      <c r="H97" t="n">
+        <v>1524</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -7729,10 +7537,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H98" t="n">
+        <v>80</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -7804,10 +7610,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="H99" t="n">
+        <v>137</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -7879,10 +7683,8 @@
           <t>172.30.1.1</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H100" t="n">
+        <v>21</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7954,10 +7756,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H101" t="n">
+        <v>0</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -8029,10 +7829,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H102" t="n">
+        <v>0</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -8104,10 +7902,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H103" t="n">
+        <v>80</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -8179,10 +7975,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H104" t="n">
+        <v>21</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -8254,10 +8048,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H105" t="n">
+        <v>22</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -8329,10 +8121,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H106" t="n">
+        <v>80</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -8404,10 +8194,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H107" t="n">
+        <v>0</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -8479,10 +8267,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H108" t="n">
+        <v>0</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -8554,10 +8340,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H109" t="n">
+        <v>0</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -8629,10 +8413,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H110" t="n">
+        <v>21</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -8704,10 +8486,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H111" t="n">
+        <v>80</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -8779,10 +8559,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H112" t="n">
+        <v>80</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -8854,10 +8632,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H113" t="n">
+        <v>0</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -8929,10 +8705,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H114" t="n">
+        <v>80</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -8956,7 +8730,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>['Response Code : HTTP/1.1 200 OK', 'Protocol version : HTTP/1.1\nHTTP/2 TLS Support: No\nHTTP/2 Cleartext Support: No\nSSL : no\nKeep-Alive : yes\nOptions allowed : (Not implemented)\nHeaders :', 'Date: Thu, 23 Jul 2026 22:31:49 GMT\n  Server: Apache/2.4.59 (Debian)\n  Last-Modified: Sat, 04 May 2024 06:53:23 GMT\n  ETag: "29cd-6179b4ad35ec0"\n  Accept-Ranges: bytes\n  Content-Length: 10701\n  Vary: Accept-Encoding\n  Keep-Alive: timeout=5, max=98\n  Connection: Keep-Alive\n  Content-Type: text/html', 'Response Body :', '&lt;!DOCTYPE html PUBLIC "-//W3C//DTD XHTML 1.0 Transitional//EN" "http://www.w3.org/TR/xhtml1/DTD/xhtml1-transitional.dtd"&gt;\n&lt;html xmlns="http://www.w3.org/1999/xhtml"&gt;\n  &lt;head&gt;\n    &lt;meta http-equiv="Content-Type" content="text/html; charset=UTF-8" /&gt;\n    &lt;title&gt;Apache2 Debian Default Page: It works&lt;/title&gt;\n    &lt;style type="text/css" media="screen"&gt;\n  * {\n    margin: 0px 0px 0px 0px;\n    padding: 0px 0px 0px 0px;\n  }', 'body, html {\n    padding: 3px 3px 3px 3px;', 'background-color: #D8DBE2;', 'font-family: Verdana, sans-serif;\n    font-size: 11pt;\n    text-align: center;\n  }', 'div.main_page {\n    position: relative;\n    display: table;', 'width: 800px;', 'margin-bottom: 3px;\n    margin-left: auto;\n    margin-right: auto;\n    padding: 0px 0px 0px 0px;', 'border-width: 2px;\n    border-color: #212738;\n    border-style: solid;', 'background-color: #FFFFFF;', 'text-align: center;\n  }', 'div.page_header {\n    height: 99px;\n    width: 100%;', 'background-color: #F5F6F7;\n  }', 'div.page_header span {\n    margin: 15px 0px 0px 50px;', 'font-size: 180%;\n    font-weight: bold;\n  }', 'div.page_header img {\n    margin: 3px 0px 0px 40px;', 'border: 0px 0px 0px;\n  }', 'div.table_of_contents {\n    clear: left;', 'min-width: 200px;', 'margin: 3px 3px 3px 3px;', 'background-color: #FFFFFF;', 'text-align: left;\n  }', 'div.table_of_contents_item {\n    clear: left;', 'width: 100%;', 'margin: 4px 0px 0px 0px;', 'background-color: #FFFFFF;', 'color: #000000;\n    text-align: left;\n  }', 'div.table_of_contents_item a {\n    margin: 6px 0px 0px 6px;\n  }', 'div.content_section {\n    margin: 3px 3px 3px 3px;', 'background-color: #FFFFFF;', 'text-align: left;\n  }', 'div.content_section_text {\n    padding: 4px 8px 4px 8px;', 'color: #000000;\n    font-size: 100%;\n  }', 'div.content_section_text pre {\n    margin: 8px 0px 8px 0px;\n    padding: 8px 8px 8px 8px;', 'border-width: 1px;\n    border-style: dotted;\n    border-color: #000000;', 'background-color: #F5F6F7;', 'font-style: italic;\n  }', 'div.content_section_text p {\n    margin-bottom: 6px;\n  }', 'div.content_section_text ul, div.content_section_text li {\n    padding: 4px 8px 4px 16px;\n  }', 'div.section_header {\n    padding: 3px 6px 3px 6px;', 'background-color: #8E9CB2;', 'color: #FFFFFF;\n    font-weight: bold;\n    font-size: 112%;\n    text-align: center;\n  }', 'div.section_header_red {\n    background-color: #CD214F;\n  }', 'div.section_header_grey {\n    background-color: #9F9386;\n  }', '.floating_element {\n    position: relative;\n    float: left;\n  }', 'div.table_of_contents_item a,\n  div.content_section_text a {\n    text-decoration: none;\n    font-weight: bold;\n  }', 'div.table_of_contents_item a:link,\n  div.table_of_contents_item a:visited,\n  div.table_of_contents_item a:active {\n    color: #000000;\n  }', 'div.table_of_contents_item a:hover {\n    background-color: #000000;', 'color: #FFFFFF;\n  }', 'div.content_section_text a:link,\n  div.content_section_text a:visited,\n   div.content_section_text a:active {\n    background-color: #DCDFE6;', 'color: #000000;\n  }', 'div.content_section_text a:hover {\n    background-color: #000000;', 'color: #DCDFE6;\n  }', 'div.validator {\n  }\n    &lt;/style&gt;\n  &lt;/head&gt;\n  &lt;body&gt;\n    &lt;div class="main_page"&gt;\n      &lt;div class="page_header floating_element"&gt;\n        &lt;img src="/icons/openlogo-75.png" alt="Debian Logo" class="floating_element"/&gt;\n        &lt;span class="floating_element"&gt;\n          Apache2 Debian Default Page\n        &lt;/span&gt;\n      &lt;/div&gt;\n&lt;!--      &lt;div class="table_of_contents floating_element"&gt;\n        &lt;div class="section_header section_header_grey"&gt;\n          TABLE OF CONTENTS\n        &lt;/div&gt;\n        &lt;div class="table_of_contents_item floating_element"&gt;\n          &lt;a href="#about"&gt;About&lt;/a&gt;\n        &lt;/div&gt;\n        &lt;div class="table_of_contents_item floating_element"&gt;\n          &lt;a href="#changes"&gt;Changes&lt;/a&gt;\n        &lt;/div&gt;\n        &lt;div class="table_of_contents_item floating_element"&gt;\n          &lt;a href="#scope"&gt;Scope&lt;/a&gt;\n        &lt;/div&gt;\n        &lt;div class="table_of_contents_item floating_element"&gt;\n          &lt;a href="#files"&gt;Config files&lt;/a&gt;\n        &lt;/div&gt;\n      &lt;/div&gt;\n--&gt;\n      &lt;div class="content_section floating_element"&gt;', '&lt;div class="section_header section_header_red"&gt;\n          &lt;div id="about"&gt;&lt;/div&gt;\n          It works!\n        &lt;/div&gt;\n        &lt;div class="content_section_text"&gt;\n          &lt;p&gt;\n                This is the default welcome page used to test the correct \n                operation of the Apache2 server after installation on Debian systems.\n                If you can read this page, it means that the Apache HTTP server installed at\n                this site is working properly. You should &lt;b&gt;replace this file&lt;/b&gt; (located at\n                &lt;tt&gt;/var/www/html/index.html&lt;/tt&gt;) before continuing to operate your HTTP server.\n          &lt;/p&gt;', "&lt;p&gt;\n                If you are a normal user of this web site and don't know what this page is\n                about, this probably means that the site is currently unavailable due to\n                maintenance.\n                If the problem persists, please contact the site's administrator.\n          &lt;/p&gt;", '&lt;/div&gt;\n        &lt;div class="section_header"&gt;\n          &lt;div id="changes"&gt;&lt;/div&gt;\n                Configuration Overview\n        &lt;/div&gt;\n        &lt;div class="content_section_text"&gt;\n          &lt;p&gt;\n                Debian\'s Apache2 default configuration is different from the\n                upstream default configuration, and split into several files optimized for\n                interaction with Debian tools. The configuration system is\n                &lt;b&gt;fully documented in\n                /usr/share/doc/apache2/README.Debian.gz&lt;/b&gt;. Refer to this for the full\n                documentation. Documentation for the web server itself can be\n                found by accessing the &lt;a href="/manual"&gt;manual&lt;/a&gt; if the &lt;tt&gt;apache2-doc&lt;/tt&gt;\n                package was installed on this server.', '&lt;/p&gt;\n          &lt;p&gt;\n                The configuration layout for an Apache2 web server installation on Debian systems is as follows:\n          &lt;/p&gt;\n          &lt;pre&gt;\n/etc/apache2/\n|-- apache2.conf\n|       `--  ports.conf\n|-- mods-enabled\n|       |-- *.load\n|       `-- *.conf\n|-- conf-enabled\n|       `-- *.conf\n|-- sites-enabled\n|       `-- *.conf\n          &lt;/pre&gt;\n          &lt;ul&gt;\n                        &lt;li&gt;\n                           &lt;tt&gt;apache2.conf&lt;/tt&gt; is the main configuration\n                           file. It puts the pieces together by including all remaining configuration\n                           files when starting up the web server.\n                        &lt;/li&gt;', '&lt;li&gt;\n                           &lt;tt&gt;ports.conf&lt;/tt&gt; is always included from the\n                           main configuration file. It is used to determine the listening ports for\n                           incoming connections, and this file can be customized anytime.\n                        &lt;/li&gt;', '&lt;li&gt;\n                           Configuration files in the &lt;tt&gt;mods-enabled/&lt;/tt&gt;,\n                           &lt;tt&gt;conf-enabled/&lt;/tt&gt; and &lt;tt&gt;sites-enabled/&lt;/tt&gt; directories contain\n                           particular configuration snippets which manage modules, global configuration\n                           fragments, or virtual host configurations, respectively.\n                        &lt;/li&gt;', '&lt;li&gt;\n                           They are activated by symlinking available\n                           configuration files from their respective\n                           *-available/ counterparts. These should be managed\n                           by using our helpers\n                           &lt;tt&gt;\n                                a2enmod,\n                                a2dismod,\n                           &lt;/tt&gt;\n                           &lt;tt&gt;\n                                a2ensite,\n                                a2dissite,\n                            &lt;/tt&gt;\n                                and\n                           &lt;tt&gt;\n                                a2enconf,\n                                a2disconf\n                           &lt;/tt&gt;. See their respective man pages for detailed information.\n                        &lt;/li&gt;', '&lt;li&gt;\n                           The binary is called apache2. Due to the use of\n                           environment variables, in the default configuration, apache2 needs to be\n                           started/stopped with &lt;tt&gt;/etc/init.d/apache2&lt;/tt&gt; or &lt;tt&gt;apache2ctl&lt;/tt&gt;.\n                           &lt;b&gt;Calling &lt;tt&gt;/usr/bin/apache2&lt;/tt&gt; directly will not work&lt;/b&gt; with the\n                           default configuration.\n                        &lt;/li&gt;\n          &lt;/ul&gt;\n        &lt;/div&gt;', '&lt;div class="section_header"&gt;\n            &lt;div id="docroot"&gt;&lt;/div&gt;\n                Document Roots\n        &lt;/div&gt;', '&lt;div class="content_section_text"&gt;\n            &lt;p&gt;\n                By default, Debian does not allow access through the web browser to\n                &lt;em&gt;any&lt;/em&gt; file apart of those located in &lt;tt&gt;/var/www&lt;/tt&gt;,\n                &lt;a href="http://httpd.apache.org/docs/2.4/mod/mod_userdir.html" rel="nofollow"&gt;public_html&lt;/a&gt;\n                directories (when enabled) and &lt;tt&gt;/usr/share&lt;/tt&gt; (for web\n                applications). If your site is using a web document root\n                located elsewhere (such as in &lt;tt&gt;/srv&lt;/tt&gt;) you may need to whitelist your\n                document root directory in &lt;tt&gt;/etc/apache2/apache2.conf&lt;/tt&gt;.\n            &lt;/p&gt;\n            &lt;p&gt;\n                The default Debian document root is &lt;tt&gt;/var/www/html&lt;/tt&gt;. You\n                can make your own virtual hosts under /var/www. This is different\n                to previous releases which provides better security out of the box.\n            &lt;/p&gt;\n        &lt;/div&gt;', '&lt;div class="section_header"&gt;\n          &lt;div id="bugs"&gt;&lt;/div&gt;\n                Reporting Problems\n        &lt;/div&gt;\n        &lt;div class="content_section_text"&gt;\n          &lt;p&gt;\n                Please use the &lt;tt&gt;reportbug&lt;/tt&gt; tool to report bugs in the\n                Apache2 package with Debian. However, check &lt;a\n                href="http://bugs.debian.org/cgi-bin/pkgreport.cgi?ordering=normal;archive=0;src=apache2;repeatmerged=0"\n                rel="nofollow"&gt;existing bug reports&lt;/a&gt; before reporting a new bug.\n          &lt;/p&gt;\n          &lt;p&gt;\n                Please report bugs specific to modules (such as PHP and others)\n                to respective packages, not to the web server itself.\n          &lt;/p&gt;\n        &lt;/div&gt;', '&lt;/div&gt;\n    &lt;/div&gt;\n    &lt;div class="validator"&gt;\n    &lt;/div&gt;\n  &lt;/body&gt;\n&lt;/html&gt;']</t>
+          <t>['Response Code : HTTP/1.1 200 OK', 'Protocol version : HTTP/1.1\nHTTP/2 TLS Support: No\nHTTP/2 Cleartext Support: No\nSSL : no\nKeep-Alive : yes\nOptions allowed : (Not implemented)\nHeaders :', 'Date: Thu, 23 Jul 2026 22:31:49 GMT\n  Server: Apache/2.4.59 (Debian)\n  Last-Modified: Sat, 04 May 2024 06:53:23 GMT\n  ETag: "29cd-6179b4ad35ec0"\n  Accept-Ranges: bytes\n  Content-Length: 10701\n  Vary: Accept-Encoding\n  Keep-Alive: timeout=5, max=98\n  Connection: Keep-Alive\n  Content-Type: text/html', 'Response Body :', '&lt;!DOCTYPE html PUBLIC "-//W3C//DTD XHTML 1.0 Transitional//EN" "http://www.w3.org/TR/xhtml1/DTD/xhtml1-transitional.dtd"&gt;\n&lt;html xmlns="http://www.w3.org/1999/xhtml"&gt;\n  &lt;head&gt;\n    &lt;meta http-equiv="Content-Type" content="text/html; charset=UTF-8" /&gt;\n    &lt;title&gt;Apache2 Debian Default Page: It works&lt;/title&gt;\n    &lt;style type="text/css" media="screen"&gt;\n  * {\n    margin: 0px 0px 0px 0px;\n    padding: 0px 0px 0px 0px;\n  }', 'body, html {\n    padding: 3px 3px 3px 3px;', 'background-color: #D8DBE2;', 'font-family: Verdana, sans-serif;\n    font-size: 11pt;\n    text-align: center;\n  }', 'div.main_page {\n    position: relative;\n    display: table;', 'width: 800px;', 'margin-bottom: 3px;\n    margin-left: auto;\n    margin-right: auto;\n    padding: 0px 0px 0px 0px;', 'border-width: 2px;\n    border-color: #212738;\n    border-style: solid;', 'background-color: #FFFFFF;', 'text-align: center;\n  }', 'div.page_header {\n    height: 99px;\n    width: 100%;', 'background-color: #F5F6F7;\n  }', 'div.page_header span {\n    margin: 15px 0px 0px 50px;', 'font-size: 180%;\n    font-weight: bold;\n  }', 'div.page_header img {\n    margin: 3px 0px 0px 40px;', 'border: 0px 0px 0px;\n  }', 'div.table_of_contents {\n    clear: left;', 'min-width: 200px;', 'margin: 3px 3px 3px 3px;', 'background-color: #FFFFFF;', 'text-align: left;\n  }', 'div.table_of_contents_item {\n    clear: left;', 'width: 100%;', 'margin: 4px 0px 0px 0px;', 'background-color: #FFFFFF;', 'color: #000000;\n    text-align: left;\n  }', 'div.table_of_contents_item a {\n    margin: 6px 0px 0px 6px;\n  }', 'div.content_section {\n    margin: 3px 3px 3px 3px;', 'background-color: #FFFFFF;', 'text-align: left;\n  }', 'color: #000000;\n    font-size: 100%;\n  }', 'background-color: #F5F6F7;', 'color: #FFFFFF;\n    font-weight: bold;\n    font-size: 112%;\n    text-align: center;\n  }', 'div.table_of_contents_item a,\n  div.content_section_text a {\n    text-decoration: none;\n    font-weight: bold;\n  }', 'div.table_of_contents_item a:hover {\n    background-color: #000000;', 'color: #FFFFFF;\n  }', 'color: #000000;\n  }']</t>
         </is>
       </c>
       <c r="N114" t="n">
@@ -9004,10 +8778,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H115" t="n">
+        <v>21</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -9079,10 +8851,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H116" t="n">
+        <v>22</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -9154,10 +8924,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H117" t="n">
+        <v>80</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -9229,10 +8997,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H118" t="n">
+        <v>0</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -9304,10 +9070,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H119" t="n">
+        <v>0</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -9379,10 +9143,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H120" t="n">
+        <v>0</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -9454,10 +9216,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H121" t="n">
+        <v>0</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -9529,10 +9289,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H122" t="n">
+        <v>22</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -9604,10 +9362,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H123" t="n">
+        <v>22</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -9679,10 +9435,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H124" t="n">
+        <v>22</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -9754,10 +9508,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H125" t="n">
+        <v>22</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -9829,10 +9581,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H126" t="n">
+        <v>22</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -9904,10 +9654,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H127" t="n">
+        <v>22</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -9979,10 +9727,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H128" t="n">
+        <v>22</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -10054,10 +9800,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H129" t="n">
+        <v>21</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -10129,10 +9873,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H130" t="n">
+        <v>22</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -10204,10 +9946,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H131" t="n">
+        <v>80</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -10279,10 +10019,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H132" t="n">
+        <v>0</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -10354,10 +10092,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H133" t="n">
+        <v>0</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -10429,10 +10165,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H134" t="n">
+        <v>0</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -10504,10 +10238,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H135" t="n">
+        <v>0</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -10579,10 +10311,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H136" t="n">
+        <v>80</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -10654,10 +10384,8 @@
           <t>172.30.2.2</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H137" t="n">
+        <v>21</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -10729,10 +10457,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H138" t="n">
+        <v>445</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -10804,10 +10530,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H139" t="n">
+        <v>0</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -10879,10 +10603,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H140" t="n">
+        <v>445</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -10954,10 +10676,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H141" t="n">
+        <v>0</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -11029,10 +10749,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H142" t="n">
+        <v>0</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -11104,10 +10822,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H143" t="n">
+        <v>0</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -11179,10 +10895,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H144" t="n">
+        <v>0</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -11254,10 +10968,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H145" t="n">
+        <v>0</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -11329,10 +11041,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H146" t="n">
+        <v>0</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -11404,10 +11114,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H147" t="n">
+        <v>445</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -11479,10 +11187,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H148" t="n">
+        <v>445</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -11554,10 +11260,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H149" t="n">
+        <v>445</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -11629,10 +11333,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H150" t="n">
+        <v>445</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -11704,10 +11406,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="H151" t="n">
+        <v>139</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -11779,10 +11479,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H152" t="n">
+        <v>445</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -11854,10 +11552,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H153" t="n">
+        <v>445</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -11929,10 +11625,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H154" t="n">
+        <v>445</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -12004,10 +11698,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H155" t="n">
+        <v>445</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -12079,10 +11771,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H156" t="n">
+        <v>445</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -12154,10 +11844,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="H157" t="n">
+        <v>139</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -12229,10 +11917,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H158" t="n">
+        <v>445</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -12304,10 +11990,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H159" t="n">
+        <v>0</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -12379,10 +12063,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H160" t="n">
+        <v>0</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -12454,10 +12136,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H161" t="n">
+        <v>0</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -12529,10 +12209,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H162" t="n">
+        <v>445</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -12604,10 +12282,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H163" t="n">
+        <v>445</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -12679,10 +12355,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H164" t="n">
+        <v>445</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -12754,10 +12428,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H165" t="n">
+        <v>0</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -12829,10 +12501,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H166" t="n">
+        <v>0</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -12904,10 +12574,8 @@
           <t>172.30.4.1</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
+      <c r="H167" t="n">
+        <v>445</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -12979,10 +12647,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H168" t="n">
+        <v>80</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -13054,10 +12720,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H169" t="n">
+        <v>0</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -13129,10 +12793,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H170" t="n">
+        <v>0</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -13204,10 +12866,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H171" t="n">
+        <v>80</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -13279,10 +12939,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H172" t="n">
+        <v>80</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -13354,10 +13012,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H173" t="n">
+        <v>0</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -13429,10 +13085,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H174" t="n">
+        <v>0</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -13504,10 +13158,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H175" t="n">
+        <v>0</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -13579,10 +13231,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H176" t="n">
+        <v>80</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -13654,10 +13304,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H177" t="n">
+        <v>80</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -13729,10 +13377,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H178" t="n">
+        <v>0</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -13804,10 +13450,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H179" t="n">
+        <v>80</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -13879,10 +13523,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H180" t="n">
+        <v>80</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -13954,10 +13596,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H181" t="n">
+        <v>0</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -14029,10 +13669,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H182" t="n">
+        <v>0</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -14104,10 +13742,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H183" t="n">
+        <v>0</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -14179,10 +13815,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H184" t="n">
+        <v>80</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -14254,10 +13888,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H185" t="n">
+        <v>0</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -14329,10 +13961,8 @@
           <t>172.30.6.3</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H186" t="n">
+        <v>0</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -14404,10 +14034,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H187" t="n">
+        <v>0</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -14479,10 +14107,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H188" t="n">
+        <v>0</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -14554,10 +14180,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H189" t="n">
+        <v>0</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -14629,10 +14253,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H190" t="n">
+        <v>0</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -14704,10 +14326,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H191" t="n">
+        <v>0</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -14779,10 +14399,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H192" t="n">
+        <v>0</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -14854,10 +14472,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
+      <c r="H193" t="n">
+        <v>3000</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -14929,10 +14545,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H194" t="n">
+        <v>0</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15004,10 +14618,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H195" t="n">
+        <v>0</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15079,10 +14691,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H196" t="n">
+        <v>0</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -15154,10 +14764,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H197" t="n">
+        <v>0</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -15229,10 +14837,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
+      <c r="H198" t="n">
+        <v>3000</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -15304,10 +14910,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
+      <c r="H199" t="n">
+        <v>3000</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -15379,10 +14983,8 @@
           <t>172.30.7.1</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
+      <c r="H200" t="n">
+        <v>3000</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -15454,10 +15056,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H201" t="n">
+        <v>0</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -15529,10 +15129,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H202" t="n">
+        <v>0</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -15604,10 +15202,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H203" t="n">
+        <v>80</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -15679,10 +15275,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H204" t="n">
+        <v>80</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -15754,10 +15348,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H205" t="n">
+        <v>0</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -15829,10 +15421,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H206" t="n">
+        <v>0</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -15904,10 +15494,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H207" t="n">
+        <v>0</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -15979,10 +15567,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H208" t="n">
+        <v>80</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -16054,10 +15640,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H209" t="n">
+        <v>0</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -16129,10 +15713,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H210" t="n">
+        <v>80</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -16204,10 +15786,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H211" t="n">
+        <v>80</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -16279,10 +15859,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H212" t="n">
+        <v>0</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -16354,10 +15932,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H213" t="n">
+        <v>0</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -16429,10 +16005,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H214" t="n">
+        <v>0</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -16504,10 +16078,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H215" t="n">
+        <v>80</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -16579,10 +16151,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H216" t="n">
+        <v>0</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -16654,10 +16224,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H217" t="n">
+        <v>0</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -16729,10 +16297,8 @@
           <t>172.30.9.1</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H218" t="n">
+        <v>80</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -16804,10 +16370,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H219" t="n">
+        <v>80</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -16879,10 +16443,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H220" t="n">
+        <v>0</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -16954,10 +16516,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H221" t="n">
+        <v>80</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17029,10 +16589,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H222" t="n">
+        <v>0</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17104,10 +16662,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H223" t="n">
+        <v>0</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17179,10 +16735,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H224" t="n">
+        <v>80</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17254,10 +16808,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H225" t="n">
+        <v>80</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -17329,10 +16881,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H226" t="n">
+        <v>80</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -17404,10 +16954,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H227" t="n">
+        <v>0</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -17479,10 +17027,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H228" t="n">
+        <v>0</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -17554,10 +17100,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H229" t="n">
+        <v>0</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -17629,10 +17173,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H230" t="n">
+        <v>80</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -17704,10 +17246,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H231" t="n">
+        <v>0</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -17779,10 +17319,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H232" t="n">
+        <v>80</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -17854,10 +17392,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H233" t="n">
+        <v>3306</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -17929,10 +17465,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H234" t="n">
+        <v>80</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -18004,10 +17538,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H235" t="n">
+        <v>3306</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -18079,10 +17611,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H236" t="n">
+        <v>0</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -18154,10 +17684,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H237" t="n">
+        <v>0</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -18229,10 +17757,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H238" t="n">
+        <v>0</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -18304,10 +17830,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H239" t="n">
+        <v>80</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -18379,10 +17903,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H240" t="n">
+        <v>80</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -18454,10 +17976,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H241" t="n">
+        <v>3306</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -18529,10 +18049,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H242" t="n">
+        <v>0</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -18604,10 +18122,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H243" t="n">
+        <v>0</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -18679,10 +18195,8 @@
           <t>172.30.9.2</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H244" t="n">
+        <v>80</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -18754,10 +18268,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H245" t="n">
+        <v>80</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -18829,10 +18341,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H246" t="n">
+        <v>0</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -18904,10 +18414,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H247" t="n">
+        <v>0</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -18979,10 +18487,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H248" t="n">
+        <v>0</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19054,10 +18560,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H249" t="n">
+        <v>80</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19129,10 +18633,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H250" t="n">
+        <v>80</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19204,10 +18706,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H251" t="n">
+        <v>80</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19279,10 +18779,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H252" t="n">
+        <v>0</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19354,10 +18852,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H253" t="n">
+        <v>0</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -19429,10 +18925,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H254" t="n">
+        <v>0</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -19504,10 +18998,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H255" t="n">
+        <v>80</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -19579,10 +19071,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H256" t="n">
+        <v>0</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -19654,10 +19144,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H257" t="n">
+        <v>80</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -19729,10 +19217,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H258" t="n">
+        <v>3306</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -19804,10 +19290,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H259" t="n">
+        <v>80</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -19879,10 +19363,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H260" t="n">
+        <v>3306</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -19954,10 +19436,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H261" t="n">
+        <v>0</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -20029,10 +19509,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H262" t="n">
+        <v>0</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
@@ -20104,10 +19582,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H263" t="n">
+        <v>0</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -20179,10 +19655,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H264" t="n">
+        <v>80</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
@@ -20254,10 +19728,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H265" t="n">
+        <v>80</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -20329,10 +19801,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
+      <c r="H266" t="n">
+        <v>3306</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -20404,10 +19874,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H267" t="n">
+        <v>0</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -20479,10 +19947,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H268" t="n">
+        <v>0</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -20554,10 +20020,8 @@
           <t>172.30.9.3</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H269" t="n">
+        <v>80</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -20629,10 +20093,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H270" t="n">
+        <v>0</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -20704,10 +20166,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H271" t="n">
+        <v>80</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -20779,10 +20239,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H272" t="n">
+        <v>80</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -20854,10 +20312,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H273" t="n">
+        <v>0</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -20929,10 +20385,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H274" t="n">
+        <v>0</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21004,10 +20458,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H275" t="n">
+        <v>0</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -21079,10 +20531,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H276" t="n">
+        <v>0</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -21154,10 +20604,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H277" t="n">
+        <v>80</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -21229,10 +20677,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H278" t="n">
+        <v>0</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21304,10 +20750,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H279" t="n">
+        <v>80</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -21379,10 +20823,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H280" t="n">
+        <v>80</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -21454,10 +20896,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H281" t="n">
+        <v>0</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -21529,10 +20969,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H282" t="n">
+        <v>0</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -21604,10 +21042,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H283" t="n">
+        <v>0</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -21679,10 +21115,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H284" t="n">
+        <v>0</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -21754,10 +21188,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H285" t="n">
+        <v>80</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -21829,10 +21261,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H286" t="n">
+        <v>0</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -21904,10 +21334,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H287" t="n">
+        <v>0</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
@@ -21979,10 +21407,8 @@
           <t>172.30.15.1</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H288" t="n">
+        <v>80</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -22054,10 +21480,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H289" t="n">
+        <v>80</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -22129,10 +21553,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H290" t="n">
+        <v>0</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -22204,10 +21626,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H291" t="n">
+        <v>0</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -22279,10 +21699,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H292" t="n">
+        <v>80</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
@@ -22354,10 +21772,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H293" t="n">
+        <v>80</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
@@ -22429,10 +21845,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H294" t="n">
+        <v>0</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
@@ -22504,10 +21918,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H295" t="n">
+        <v>0</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -22579,10 +21991,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H296" t="n">
+        <v>0</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
@@ -22654,10 +22064,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H297" t="n">
+        <v>80</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -22729,10 +22137,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H298" t="n">
+        <v>80</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
@@ -22804,10 +22210,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H299" t="n">
+        <v>0</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -22879,10 +22283,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H300" t="n">
+        <v>80</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -22954,10 +22356,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H301" t="n">
+        <v>80</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -23029,10 +22429,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H302" t="n">
+        <v>0</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
@@ -23104,10 +22502,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H303" t="n">
+        <v>0</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
@@ -23179,10 +22575,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H304" t="n">
+        <v>0</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -23254,10 +22648,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H305" t="n">
+        <v>80</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -23329,10 +22721,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H306" t="n">
+        <v>80</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -23404,10 +22794,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H307" t="n">
+        <v>0</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
@@ -23479,10 +22867,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H308" t="n">
+        <v>0</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
@@ -23554,10 +22940,8 @@
           <t>172.30.15.2</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H309" t="n">
+        <v>80</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -23629,10 +23013,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="H310" t="n">
+        <v>161</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -23704,10 +23086,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H311" t="n">
+        <v>0</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -23779,10 +23159,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="H312" t="n">
+        <v>161</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -23854,10 +23232,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H313" t="n">
+        <v>0</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -23929,10 +23305,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H314" t="n">
+        <v>0</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -24004,10 +23378,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H315" t="n">
+        <v>0</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -24079,10 +23451,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H316" t="n">
+        <v>0</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -24154,10 +23524,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H317" t="n">
+        <v>0</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -24229,10 +23597,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H318" t="n">
+        <v>0</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -24304,10 +23670,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H319" t="n">
+        <v>0</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
@@ -24379,10 +23743,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H320" t="n">
+        <v>0</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
@@ -24454,10 +23816,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="H321" t="n">
+        <v>161</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
@@ -24529,10 +23889,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="H322" t="n">
+        <v>161</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -24604,10 +23962,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="H323" t="n">
+        <v>161</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -24679,10 +24035,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="H324" t="n">
+        <v>161</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -24754,10 +24108,8 @@
           <t>172.30.30.1</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H325" t="n">
+        <v>0</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
@@ -24829,10 +24181,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H326" t="n">
+        <v>80</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
@@ -24904,10 +24254,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H327" t="n">
+        <v>0</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -24979,10 +24327,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H328" t="n">
+        <v>0</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
@@ -25054,10 +24400,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H329" t="n">
+        <v>0</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
@@ -25129,10 +24473,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H330" t="n">
+        <v>80</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
@@ -25204,10 +24546,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H331" t="n">
+        <v>80</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -25279,10 +24619,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H332" t="n">
+        <v>0</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -25354,10 +24692,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H333" t="n">
+        <v>0</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25429,10 +24765,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H334" t="n">
+        <v>0</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25504,10 +24838,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H335" t="n">
+        <v>80</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -25579,10 +24911,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H336" t="n">
+        <v>80</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -25654,10 +24984,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H337" t="n">
+        <v>0</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -25729,10 +25057,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H338" t="n">
+        <v>80</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -25804,10 +25130,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H339" t="n">
+        <v>80</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -25879,10 +25203,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H340" t="n">
+        <v>0</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -25954,10 +25276,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H341" t="n">
+        <v>0</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -26029,10 +25349,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H342" t="n">
+        <v>0</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -26104,10 +25422,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H343" t="n">
+        <v>80</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -26179,10 +25495,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H344" t="n">
+        <v>0</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -26254,10 +25568,8 @@
           <t>172.30.40.7</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H345" t="n">
+        <v>0</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -26329,10 +25641,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H346" t="n">
+        <v>80</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -26404,10 +25714,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
+      <c r="H347" t="n">
+        <v>443</v>
       </c>
       <c r="I347" t="inlineStr">
         <is>
@@ -26479,10 +25787,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H348" t="n">
+        <v>0</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
@@ -26554,10 +25860,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H349" t="n">
+        <v>0</v>
       </c>
       <c r="I349" t="inlineStr">
         <is>
@@ -26629,10 +25933,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H350" t="n">
+        <v>0</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -26704,10 +26006,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H351" t="n">
+        <v>80</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
@@ -26779,10 +26079,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
+      <c r="H352" t="n">
+        <v>443</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
@@ -26854,10 +26152,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H353" t="n">
+        <v>80</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
@@ -26929,10 +26225,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
+      <c r="H354" t="n">
+        <v>443</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
@@ -27004,10 +26298,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H355" t="n">
+        <v>0</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
@@ -27079,10 +26371,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H356" t="n">
+        <v>0</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
@@ -27154,10 +26444,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H357" t="n">
+        <v>0</v>
       </c>
       <c r="I357" t="inlineStr">
         <is>
@@ -27229,10 +26517,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H358" t="n">
+        <v>80</v>
       </c>
       <c r="I358" t="inlineStr">
         <is>
@@ -27304,10 +26590,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
+      <c r="H359" t="n">
+        <v>443</v>
       </c>
       <c r="I359" t="inlineStr">
         <is>
@@ -27379,10 +26663,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H360" t="n">
+        <v>80</v>
       </c>
       <c r="I360" t="inlineStr">
         <is>
@@ -27454,10 +26736,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
+      <c r="H361" t="n">
+        <v>443</v>
       </c>
       <c r="I361" t="inlineStr">
         <is>
@@ -27529,10 +26809,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H362" t="n">
+        <v>0</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
@@ -27604,10 +26882,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H363" t="n">
+        <v>80</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -27679,10 +26955,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
+      <c r="H364" t="n">
+        <v>443</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -27754,10 +27028,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H365" t="n">
+        <v>80</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27829,10 +27101,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
+      <c r="H366" t="n">
+        <v>443</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -27904,10 +27174,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H367" t="n">
+        <v>0</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -27979,10 +27247,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H368" t="n">
+        <v>0</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28054,10 +27320,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H369" t="n">
+        <v>0</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28129,10 +27393,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H370" t="n">
+        <v>80</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -28204,10 +27466,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
+      <c r="H371" t="n">
+        <v>443</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -28279,10 +27539,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H372" t="n">
+        <v>0</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -28354,10 +27612,8 @@
           <t>172.30.40.8</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H373" t="n">
+        <v>0</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28429,10 +27685,8 @@
           <t>172.31.1.1</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H374" t="n">
+        <v>0</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28504,10 +27758,8 @@
           <t>172.31.1.1</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H375" t="n">
+        <v>0</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28579,10 +27831,8 @@
           <t>172.31.1.1</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H376" t="n">
+        <v>0</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28654,10 +27904,8 @@
           <t>172.31.1.1</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H377" t="n">
+        <v>0</v>
       </c>
       <c r="I377" t="inlineStr">
         <is>
@@ -28729,10 +27977,8 @@
           <t>172.31.1.1</t>
         </is>
       </c>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H378" t="n">
+        <v>0</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
@@ -28804,10 +28050,8 @@
           <t>172.31.1.1</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H379" t="n">
+        <v>0</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
@@ -28879,10 +28123,8 @@
           <t>172.31.1.3</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H380" t="n">
+        <v>0</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
@@ -28954,10 +28196,8 @@
           <t>172.31.1.3</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H381" t="n">
+        <v>0</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
@@ -29029,10 +28269,8 @@
           <t>172.31.1.3</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H382" t="n">
+        <v>0</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
@@ -29104,10 +28342,8 @@
           <t>172.31.1.3</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H383" t="n">
+        <v>0</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
@@ -29179,10 +28415,8 @@
           <t>172.31.1.3</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H384" t="n">
+        <v>0</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
@@ -29254,10 +28488,8 @@
           <t>172.31.1.3</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H385" t="n">
+        <v>0</v>
       </c>
       <c r="I385" t="inlineStr">
         <is>
@@ -29329,10 +28561,8 @@
           <t>172.31.1.5</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H386" t="n">
+        <v>0</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
@@ -29404,10 +28634,8 @@
           <t>172.31.1.5</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H387" t="n">
+        <v>0</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
@@ -29479,10 +28707,8 @@
           <t>172.31.1.5</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H388" t="n">
+        <v>0</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -29554,10 +28780,8 @@
           <t>172.31.1.5</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H389" t="n">
+        <v>0</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -29629,10 +28853,8 @@
           <t>172.31.1.5</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H390" t="n">
+        <v>0</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -29704,10 +28926,8 @@
           <t>172.31.1.5</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H391" t="n">
+        <v>0</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -29779,10 +28999,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H392" t="n">
+        <v>0</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -29854,10 +29072,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H393" t="n">
+        <v>0</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -29929,10 +29145,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H394" t="n">
+        <v>0</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30004,10 +29218,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H395" t="n">
+        <v>0</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -30079,10 +29291,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H396" t="n">
+        <v>0</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -30154,10 +29364,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H397" t="n">
+        <v>0</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -30229,10 +29437,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>8081</t>
-        </is>
+      <c r="H398" t="n">
+        <v>8081</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -30304,10 +29510,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H399" t="n">
+        <v>0</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -30379,10 +29583,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr">
-        <is>
-          <t>8081</t>
-        </is>
+      <c r="H400" t="n">
+        <v>8081</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -30454,10 +29656,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>8081</t>
-        </is>
+      <c r="H401" t="n">
+        <v>8081</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -30529,10 +29729,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H402" t="n">
+        <v>0</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -30604,10 +29802,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H403" t="n">
+        <v>0</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30679,10 +29875,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H404" t="n">
+        <v>0</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30754,10 +29948,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr">
-        <is>
-          <t>8081</t>
-        </is>
+      <c r="H405" t="n">
+        <v>8081</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30829,10 +30021,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>8081</t>
-        </is>
+      <c r="H406" t="n">
+        <v>8081</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -30904,10 +30094,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H407" t="n">
+        <v>0</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -30979,10 +30167,8 @@
           <t>172.31.1.50</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H408" t="n">
+        <v>0</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
@@ -31054,10 +30240,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H409" t="n">
+        <v>0</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
@@ -31129,10 +30313,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H410" t="n">
+        <v>0</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
@@ -31204,10 +30386,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H411" t="n">
+        <v>21</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
@@ -31279,10 +30459,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H412" t="n">
+        <v>0</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
@@ -31354,10 +30532,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H413" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
@@ -31429,10 +30605,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H414" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
@@ -31504,10 +30678,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H415" t="n">
+        <v>21</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
@@ -31579,10 +30751,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H416" t="n">
+        <v>0</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
@@ -31654,10 +30824,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H417" t="n">
+        <v>21</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -31729,10 +30897,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H418" t="n">
+        <v>0</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -31804,10 +30970,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H419" t="n">
+        <v>0</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -31879,10 +31043,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H420" t="n">
+        <v>0</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -31954,10 +31116,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H421" t="n">
+        <v>21</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -32029,10 +31189,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H422" t="n">
+        <v>0</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -32104,10 +31262,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="H423" t="n">
+        <v>0</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32179,10 +31335,8 @@
           <t>172.31.1.97</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H424" t="n">
+        <v>21</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
